--- a/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_MMPP/param_sensitivity_p99_1Mbps.xlsx
+++ b/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_MMPP/param_sensitivity_p99_1Mbps.xlsx
@@ -45,14 +45,14 @@
       <color rgb="00F0F6FC"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="0056D364"/>
+    </font>
+    <font>
       <color rgb="00F0F6FC"/>
     </font>
     <font>
       <color rgb="008B949E"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0056D364"/>
     </font>
     <font>
       <b val="1"/>
@@ -83,17 +83,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00161B22"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="000D2B1A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000F1117"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00161B22"/>
       </patternFill>
     </fill>
     <fill>
@@ -139,88 +139,88 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>19944.9</v>
+        <v>22307.2</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>20076</v>
+        <v>22648</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>-0.015</v>
+        <v>0.036</v>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
@@ -689,13 +689,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>13651.1</v>
+        <v>15625</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>22459.7</v>
+        <v>25124.7</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.613</v>
+        <v>0.579</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -718,13 +718,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>19461.1</v>
+        <v>21594.6</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>20315.8</v>
+        <v>23146.8</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.073</v>
+        <v>0.095</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>18347.4</v>
+        <v>20699.6</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>18357.1</v>
+        <v>20781.8</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18137.5</v>
+        <v>20540.8</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>18481.7</v>
+        <v>20912.5</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.1</v>
+        <v>-0.116</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>18236.7</v>
+        <v>20480.8</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>18459.2</v>
+        <v>20995.2</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.097</v>
+        <v>0.159</v>
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>no clear trend (≈flat)</t>
+          <t>mildly: larger param → larger delay</t>
         </is>
       </c>
     </row>
@@ -1104,64 +1104,64 @@
       <c r="A5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="21" t="n">
-        <v>20076</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>5592.5</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>29382.5</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>17750.3</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>19925.6</v>
-      </c>
-      <c r="G5" s="21" t="n">
-        <v>22552.2</v>
-      </c>
-      <c r="H5" s="22" t="n">
+      <c r="B5" s="13" t="n">
+        <v>22307.2</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>10727.5</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>32352.5</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>19617.8</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>22574.7</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>24729.2</v>
+      </c>
+      <c r="H5" s="21" t="n">
         <v>108</v>
       </c>
-      <c r="I5" s="23" t="inlineStr"/>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>◀ best (min P99)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="n">
+      <c r="A6" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="13" t="n">
-        <v>19944.9</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>6197.5</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>29432.5</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>17517.2</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>20176.4</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>22141.1</v>
+      <c r="B6" s="24" t="n">
+        <v>22648</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>9962.5</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>33372.5</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>20068.6</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>22652.5</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>25222.8</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>108</v>
       </c>
-      <c r="I6" s="26" t="inlineStr">
-        <is>
-          <t>◀ best (min P99)</t>
-        </is>
-      </c>
+      <c r="I6" s="26" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.015   |   no clear trend (≈flat)   |   recommended CWds = 1 (lowest mean P99 = 19945 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.036   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 22307 µs)</t>
         </is>
       </c>
     </row>
@@ -1216,175 +1216,175 @@
       <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="20" t="n">
         <v>0</v>
       </c>
       <c r="B11" s="13" t="n">
-        <v>13651.1</v>
+        <v>15625</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>5592.5</v>
+        <v>9962.5</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>18407.5</v>
+        <v>19872.5</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>11624.2</v>
+        <v>14069.2</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>14345</v>
+        <v>16089.2</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>14984.2</v>
-      </c>
-      <c r="H11" s="25" t="n">
+        <v>16716.7</v>
+      </c>
+      <c r="H11" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>◀ best (min P99)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="n">
+      <c r="A12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="29" t="n">
-        <v>17914.2</v>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>13967.5</v>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>23692.5</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>15976.7</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>18300.8</v>
-      </c>
-      <c r="G12" s="29" t="n">
-        <v>19465</v>
-      </c>
-      <c r="H12" s="30" t="n">
+      <c r="B12" s="24" t="n">
+        <v>20571.9</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>14177.5</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>27187.5</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>17933.3</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>21065.8</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>22716.7</v>
+      </c>
+      <c r="H12" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="I12" s="31" t="inlineStr"/>
+      <c r="I12" s="26" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="21" t="n">
-        <v>21699.4</v>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>17652.5</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>28667.5</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>18824.2</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>21263.3</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>25010.8</v>
-      </c>
-      <c r="H13" s="22" t="n">
+      <c r="B13" s="29" t="n">
+        <v>24481.1</v>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>17437.5</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>33372.5</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>20389.2</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>24377.5</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>28676.7</v>
+      </c>
+      <c r="H13" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="I13" s="23" t="inlineStr"/>
+      <c r="I13" s="31" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="n">
+      <c r="A14" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>22321.7</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>16712.5</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>29432.5</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>19515</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>21693.3</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>25756.7</v>
-      </c>
-      <c r="H14" s="30" t="n">
+      <c r="B14" s="24" t="n">
+        <v>25124.7</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>21037.5</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>31732.5</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>22845</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>24155.8</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>28373.3</v>
+      </c>
+      <c r="H14" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="I14" s="31" t="inlineStr"/>
+      <c r="I14" s="26" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="21" t="n">
-        <v>22459.7</v>
-      </c>
-      <c r="C15" s="21" t="n">
-        <v>18727.5</v>
-      </c>
-      <c r="D15" s="21" t="n">
-        <v>29382.5</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>20251.7</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>22226.7</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>24900.8</v>
-      </c>
-      <c r="H15" s="22" t="n">
+      <c r="B15" s="29" t="n">
+        <v>25040</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>20392.5</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>31752.5</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>21708.3</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>25655</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>27756.7</v>
+      </c>
+      <c r="H15" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="I15" s="23" t="inlineStr"/>
+      <c r="I15" s="31" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="n">
+      <c r="A16" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="29" t="n">
-        <v>22016.7</v>
-      </c>
-      <c r="C16" s="29" t="n">
-        <v>18547.5</v>
-      </c>
-      <c r="D16" s="29" t="n">
-        <v>28477.5</v>
-      </c>
-      <c r="E16" s="29" t="n">
-        <v>19610.8</v>
-      </c>
-      <c r="F16" s="29" t="n">
-        <v>22476.7</v>
-      </c>
-      <c r="G16" s="29" t="n">
-        <v>23962.5</v>
-      </c>
-      <c r="H16" s="30" t="n">
+      <c r="B16" s="24" t="n">
+        <v>24022.8</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>20122.5</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>28762.5</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>22114.2</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>24338.3</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>25615.8</v>
+      </c>
+      <c r="H16" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="I16" s="31" t="inlineStr"/>
+      <c r="I16" s="26" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.613   |   strongly: larger param → larger delay   |   recommended QSRC = 0 (lowest mean P99 = 13651 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.579   |   strongly: larger param → larger delay   |   recommended QSRC = 0 (lowest mean P99 = 15625 µs)</t>
         </is>
       </c>
     </row>
@@ -1439,94 +1439,94 @@
       <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="n">
+      <c r="A21" s="20" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="13" t="n">
-        <v>19461.1</v>
+        <v>21594.6</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>15777.5</v>
+        <v>17507.5</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>22547.5</v>
+        <v>25322.5</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>17989.6</v>
+        <v>19843.3</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>19439.2</v>
+        <v>21625</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>20954.6</v>
-      </c>
-      <c r="H21" s="25" t="n">
+        <v>23315.4</v>
+      </c>
+      <c r="H21" s="21" t="n">
         <v>72</v>
       </c>
-      <c r="I21" s="26" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>◀ best (min P99)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="n">
+      <c r="A22" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="29" t="n">
-        <v>20315.8</v>
-      </c>
-      <c r="C22" s="29" t="n">
-        <v>13082.5</v>
-      </c>
-      <c r="D22" s="29" t="n">
-        <v>26247.5</v>
-      </c>
-      <c r="E22" s="29" t="n">
-        <v>17751.7</v>
-      </c>
-      <c r="F22" s="29" t="n">
-        <v>19890</v>
-      </c>
-      <c r="G22" s="29" t="n">
-        <v>23305.8</v>
-      </c>
-      <c r="H22" s="30" t="n">
+      <c r="B22" s="24" t="n">
+        <v>23146.8</v>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>13642.5</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>29157.5</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>20281.7</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>22888.3</v>
+      </c>
+      <c r="G22" s="24" t="n">
+        <v>26270.4</v>
+      </c>
+      <c r="H22" s="25" t="n">
         <v>72</v>
       </c>
-      <c r="I22" s="31" t="inlineStr"/>
+      <c r="I22" s="26" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="n">
+      <c r="A23" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="21" t="n">
-        <v>20254.4</v>
-      </c>
-      <c r="C23" s="21" t="n">
-        <v>5592.5</v>
-      </c>
-      <c r="D23" s="21" t="n">
-        <v>29432.5</v>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>17160</v>
-      </c>
-      <c r="F23" s="21" t="n">
-        <v>20823.8</v>
-      </c>
-      <c r="G23" s="21" t="n">
-        <v>22779.6</v>
-      </c>
-      <c r="H23" s="22" t="n">
+      <c r="B23" s="29" t="n">
+        <v>22691.4</v>
+      </c>
+      <c r="C23" s="29" t="n">
+        <v>9962.5</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>33372.5</v>
+      </c>
+      <c r="E23" s="29" t="n">
+        <v>19404.6</v>
+      </c>
+      <c r="F23" s="29" t="n">
+        <v>23327.5</v>
+      </c>
+      <c r="G23" s="29" t="n">
+        <v>25342.1</v>
+      </c>
+      <c r="H23" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="I23" s="23" t="inlineStr"/>
+      <c r="I23" s="31" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.073   |   no clear trend (≈flat)   |   recommended PSRC = 1 (lowest mean P99 = 19461 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.095   |   no clear trend (≈flat)   |   recommended PSRC = 1 (lowest mean P99 = 21595 µs)</t>
         </is>
       </c>
     </row>
@@ -1622,71 +1622,71 @@
       <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="n">
+      <c r="A5" s="20" t="n">
         <v>0</v>
       </c>
       <c r="B5" s="13" t="n">
-        <v>18347.4</v>
+        <v>20699.6</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>16977.5</v>
+        <v>19547.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>19252.5</v>
+        <v>22467.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>18149.4</v>
+        <v>20277.2</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>18545.3</v>
+        <v>21121.9</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="25" t="n">
+      <c r="H5" s="21" t="n">
         <v>72</v>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>◀ best (min P99)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n">
+      <c r="A6" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="29" t="n">
-        <v>18357.1</v>
-      </c>
-      <c r="C6" s="29" t="n">
-        <v>17167.5</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>19687.5</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>17988.6</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>18725.6</v>
-      </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="B6" s="24" t="n">
+        <v>20781.8</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>19522.5</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>22027.5</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>20457.8</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>21105.8</v>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="30" t="n">
+      <c r="H6" s="25" t="n">
         <v>72</v>
       </c>
-      <c r="I6" s="31" t="inlineStr"/>
+      <c r="I6" s="26" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.009   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 18347 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.061   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 20700 µs)</t>
         </is>
       </c>
     </row>
@@ -1741,187 +1741,187 @@
       <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>18137.5</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>16977.5</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>19127.5</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>17875.8</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>18399.2</v>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="B11" s="29" t="n">
+        <v>20800</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>19977.5</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>21852.5</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>20704.2</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>20895.8</v>
+      </c>
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="25" t="n">
+      <c r="H11" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I11" s="31" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>20912.5</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>20037.5</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>21737.5</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>20633.3</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>21191.7</v>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="I12" s="26" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="29" t="n">
+        <v>20795.8</v>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>19627.5</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>22467.5</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>20412.5</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>21179.2</v>
+      </c>
+      <c r="G13" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>24</v>
+      </c>
+      <c r="I13" s="31" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>20540.8</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>19547.5</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>21942.5</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>19952.5</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>21129.2</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>◀ best (min P99)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>18347.9</v>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>18027.5</v>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>18727.5</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>18307.5</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>18388.3</v>
-      </c>
-      <c r="G12" s="29" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="29" t="n">
+        <v>20797.1</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>19522.5</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>22027.5</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>19975</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>21619.2</v>
+      </c>
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="30" t="n">
+      <c r="H15" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="I12" s="31" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="21" t="n">
-        <v>18481.7</v>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>17732.5</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>19232.5</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>18173.3</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>18790</v>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="I15" s="31" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>20597.9</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>19922.5</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>21352.5</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>20527.5</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>20668.3</v>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="22" t="n">
+      <c r="H16" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="I13" s="23" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" s="29" t="n">
-        <v>18389.2</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>17697.5</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>19687.5</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>18026.7</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>18751.7</v>
-      </c>
-      <c r="G14" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="I14" s="31" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="21" t="n">
-        <v>18448.8</v>
-      </c>
-      <c r="C15" s="21" t="n">
-        <v>17837.5</v>
-      </c>
-      <c r="D15" s="21" t="n">
-        <v>19397.5</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>18165.8</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>18731.7</v>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" s="29" t="n">
-        <v>18308.3</v>
-      </c>
-      <c r="C16" s="29" t="n">
-        <v>17532.5</v>
-      </c>
-      <c r="D16" s="29" t="n">
-        <v>19327.5</v>
-      </c>
-      <c r="E16" s="29" t="n">
-        <v>17865</v>
-      </c>
-      <c r="F16" s="29" t="n">
-        <v>18751.7</v>
-      </c>
-      <c r="G16" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="I16" s="31" t="inlineStr"/>
+      <c r="I16" s="26" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.100   |   no clear trend (≈flat)   |   recommended QSRC = 0 (lowest mean P99 = 18138 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.116   |   no clear trend (≈flat)   |   recommended QSRC = 3 (lowest mean P99 = 20541 µs)</t>
         </is>
       </c>
     </row>
@@ -1979,97 +1979,97 @@
       <c r="A21" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="21" t="n">
-        <v>18360.8</v>
-      </c>
-      <c r="C21" s="21" t="n">
-        <v>17652.5</v>
-      </c>
-      <c r="D21" s="21" t="n">
-        <v>19327.5</v>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>18086.7</v>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>18635</v>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="B21" s="13" t="n">
+        <v>20480.8</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>19652.5</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>21587.5</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>20285.8</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>20675.8</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="22" t="n">
+      <c r="H21" s="21" t="n">
         <v>48</v>
       </c>
-      <c r="I21" s="23" t="inlineStr"/>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>◀ best (min P99)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="n">
+      <c r="A22" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="29" t="n">
-        <v>18459.2</v>
-      </c>
-      <c r="C22" s="29" t="n">
-        <v>17532.5</v>
-      </c>
-      <c r="D22" s="29" t="n">
-        <v>19397.5</v>
-      </c>
-      <c r="E22" s="29" t="n">
-        <v>18325.8</v>
-      </c>
-      <c r="F22" s="29" t="n">
-        <v>18592.5</v>
-      </c>
-      <c r="G22" s="29" t="inlineStr">
+      <c r="B22" s="24" t="n">
+        <v>20995.2</v>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>19717.5</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>22467.5</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>20479.6</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>21510.8</v>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="30" t="n">
+      <c r="H22" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="I22" s="31" t="inlineStr"/>
+      <c r="I22" s="26" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="n">
+      <c r="A23" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="13" t="n">
-        <v>18236.7</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>16977.5</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>19687.5</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>17794.6</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>18678.8</v>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="B23" s="29" t="n">
+        <v>20746</v>
+      </c>
+      <c r="C23" s="29" t="n">
+        <v>19522.5</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>22027.5</v>
+      </c>
+      <c r="E23" s="29" t="n">
+        <v>20337.1</v>
+      </c>
+      <c r="F23" s="29" t="n">
+        <v>21155</v>
+      </c>
+      <c r="G23" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="25" t="n">
+      <c r="H23" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="I23" s="26" t="inlineStr">
-        <is>
-          <t>◀ best (min P99)</t>
-        </is>
-      </c>
+      <c r="I23" s="31" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.097   |   no clear trend (≈flat)   |   recommended PSRC = 3 (lowest mean P99 = 18237 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.159   |   mildly: larger param → larger delay   |   recommended PSRC = 1 (lowest mean P99 = 20481 µs)</t>
         </is>
       </c>
     </row>
